--- a/Excels/Excels/__enums__.xlsx
+++ b/Excels/Excels/__enums__.xlsx
@@ -3227,7 +3227,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L34"/>
+  <dimension ref="A1:L37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" style="22" min="1" max="1"/>
@@ -3285,10 +3285,6 @@
           <t>*items</t>
         </is>
       </c>
-      <c r="I1" s="40" t="n"/>
-      <c r="J1" s="40" t="n"/>
-      <c r="K1" s="40" t="n"/>
-      <c r="L1" s="40" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="41" t="inlineStr">
@@ -3375,116 +3371,116 @@
       <c r="L3" s="42" t="n"/>
     </row>
     <row r="4">
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="32" t="inlineStr">
         <is>
           <t>Battle.EffectType</t>
         </is>
       </c>
-      <c r="C4" t="b">
+      <c r="C4" s="32" t="b">
         <v>0</v>
       </c>
-      <c r="D4" t="b">
+      <c r="D4" s="32" t="b">
         <v>1</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="32" t="inlineStr">
         <is>
           <t>效果类型</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="32" t="inlineStr">
         <is>
           <t>Null</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" s="32" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="J4" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K4" s="32" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="32" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="32" t="inlineStr">
         <is>
           <t>伤害</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="J5" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K5" s="32" t="inlineStr">
         <is>
           <t>造成伤害</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="32" t="inlineStr">
         <is>
           <t>Heal</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" s="32" t="inlineStr">
         <is>
           <t>回血</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="J6" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K6" s="32" t="inlineStr">
         <is>
           <t>回复生命</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="H7" t="inlineStr">
+      <c r="H7" s="32" t="inlineStr">
         <is>
           <t>AddBuff</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" s="32" t="inlineStr">
         <is>
           <t>添加Buff</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="J7" s="32" t="n">
         <v>3</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K7" s="32" t="inlineStr">
         <is>
           <t>添加Buff</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="H8" t="inlineStr">
+      <c r="H8" s="32" t="inlineStr">
         <is>
           <t>Projectile</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I8" s="32" t="inlineStr">
         <is>
           <t>抛射物</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="J8" s="32" t="n">
         <v>4</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K8" s="32" t="inlineStr">
         <is>
           <t>发射抛射物</t>
         </is>
@@ -3492,136 +3488,136 @@
     </row>
     <row r="9"/>
     <row r="10">
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="32" t="inlineStr">
         <is>
           <t>Battle.SkillTargetType</t>
         </is>
       </c>
-      <c r="C10" t="b">
+      <c r="C10" s="32" t="b">
         <v>0</v>
       </c>
-      <c r="D10" t="b">
+      <c r="D10" s="32" t="b">
         <v>1</v>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="32" t="inlineStr">
         <is>
           <t>技能目标类型</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H10" s="32" t="inlineStr">
         <is>
           <t>Null</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I10" s="32" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="J10" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K10" s="32" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="H11" t="inlineStr">
+      <c r="H11" s="32" t="inlineStr">
         <is>
           <t>Self</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I11" s="32" t="inlineStr">
         <is>
           <t>自身</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="J11" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K11" s="32" t="inlineStr">
         <is>
           <t>自身</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="H12" t="inlineStr">
+      <c r="H12" s="32" t="inlineStr">
         <is>
           <t>Enemy</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I12" s="32" t="inlineStr">
         <is>
           <t>敌方</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="J12" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="K12" s="32" t="inlineStr">
         <is>
           <t>敌方</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="H13" t="inlineStr">
+      <c r="H13" s="32" t="inlineStr">
         <is>
           <t>Ally</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I13" s="32" t="inlineStr">
         <is>
           <t>友方</t>
         </is>
       </c>
-      <c r="J13" t="n">
+      <c r="J13" s="32" t="n">
         <v>3</v>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="K13" s="32" t="inlineStr">
         <is>
           <t>友方</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="H14" t="inlineStr">
+      <c r="H14" s="32" t="inlineStr">
         <is>
           <t>Position</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I14" s="32" t="inlineStr">
         <is>
           <t>位置</t>
         </is>
       </c>
-      <c r="J14" t="n">
+      <c r="J14" s="32" t="n">
         <v>4</v>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="K14" s="32" t="inlineStr">
         <is>
           <t>指定位置</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="H15" t="inlineStr">
+      <c r="H15" s="32" t="inlineStr">
         <is>
           <t>Direction</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I15" s="32" t="inlineStr">
         <is>
           <t>方向</t>
         </is>
       </c>
-      <c r="J15" t="n">
+      <c r="J15" s="32" t="n">
         <v>5</v>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="K15" s="32" t="inlineStr">
         <is>
           <t>指定方向</t>
         </is>
@@ -3629,136 +3625,136 @@
     </row>
     <row r="16"/>
     <row r="17">
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="32" t="inlineStr">
         <is>
           <t>Battle.TargetSelectType</t>
         </is>
       </c>
-      <c r="C17" t="b">
+      <c r="C17" s="32" t="b">
         <v>0</v>
       </c>
-      <c r="D17" t="b">
+      <c r="D17" s="32" t="b">
         <v>1</v>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" s="32" t="inlineStr">
         <is>
           <t>目标选择类型</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H17" s="32" t="inlineStr">
         <is>
           <t>Null</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I17" s="32" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="J17" t="n">
+      <c r="J17" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="K17" s="32" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="H18" t="inlineStr">
+      <c r="H18" s="32" t="inlineStr">
         <is>
           <t>Nearest</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I18" s="32" t="inlineStr">
         <is>
           <t>最近</t>
         </is>
       </c>
-      <c r="J18" t="n">
+      <c r="J18" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="K18" s="32" t="inlineStr">
         <is>
           <t>最近目标</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="H19" t="inlineStr">
+      <c r="H19" s="32" t="inlineStr">
         <is>
           <t>Random</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I19" s="32" t="inlineStr">
         <is>
           <t>随机</t>
         </is>
       </c>
-      <c r="J19" t="n">
+      <c r="J19" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="K19" s="32" t="inlineStr">
         <is>
           <t>随机目标</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="H20" t="inlineStr">
+      <c r="H20" s="32" t="inlineStr">
         <is>
           <t>LowestHp</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I20" s="32" t="inlineStr">
         <is>
           <t>最低血量</t>
         </is>
       </c>
-      <c r="J20" t="n">
+      <c r="J20" s="32" t="n">
         <v>3</v>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="K20" s="32" t="inlineStr">
         <is>
           <t>最低血量目标</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="H21" t="inlineStr">
+      <c r="H21" s="32" t="inlineStr">
         <is>
           <t>SelfAround</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I21" s="32" t="inlineStr">
         <is>
           <t>自身周围</t>
         </is>
       </c>
-      <c r="J21" t="n">
+      <c r="J21" s="32" t="n">
         <v>4</v>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="K21" s="32" t="inlineStr">
         <is>
           <t>以自身为中心</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="H22" t="inlineStr">
+      <c r="H22" s="32" t="inlineStr">
         <is>
           <t>Forward</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I22" s="32" t="inlineStr">
         <is>
           <t>前方</t>
         </is>
       </c>
-      <c r="J22" t="n">
+      <c r="J22" s="32" t="n">
         <v>5</v>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="K22" s="32" t="inlineStr">
         <is>
           <t>朝向前方</t>
         </is>
@@ -3766,116 +3762,116 @@
     </row>
     <row r="23"/>
     <row r="24">
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="32" t="inlineStr">
         <is>
           <t>Battle.SkillShapeType</t>
         </is>
       </c>
-      <c r="C24" t="b">
+      <c r="C24" s="32" t="b">
         <v>0</v>
       </c>
-      <c r="D24" t="b">
+      <c r="D24" s="32" t="b">
         <v>1</v>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F24" s="32" t="inlineStr">
         <is>
           <t>技能形状类型</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H24" s="32" t="inlineStr">
         <is>
           <t>Null</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I24" s="32" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="J24" t="n">
+      <c r="J24" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="K24" s="32" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="H25" t="inlineStr">
+      <c r="H25" s="32" t="inlineStr">
         <is>
           <t>Circle</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="I25" s="32" t="inlineStr">
         <is>
           <t>圆形</t>
         </is>
       </c>
-      <c r="J25" t="n">
+      <c r="J25" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="K25" s="32" t="inlineStr">
         <is>
           <t>圆形</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="H26" t="inlineStr">
+      <c r="H26" s="32" t="inlineStr">
         <is>
           <t>Rect</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I26" s="32" t="inlineStr">
         <is>
           <t>矩形</t>
         </is>
       </c>
-      <c r="J26" t="n">
+      <c r="J26" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="K26" s="32" t="inlineStr">
         <is>
           <t>矩形</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="H27" t="inlineStr">
+      <c r="H27" s="32" t="inlineStr">
         <is>
           <t>Sector</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="I27" s="32" t="inlineStr">
         <is>
           <t>扇形</t>
         </is>
       </c>
-      <c r="J27" t="n">
+      <c r="J27" s="32" t="n">
         <v>3</v>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="K27" s="32" t="inlineStr">
         <is>
           <t>扇形</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="H28" t="inlineStr">
+      <c r="H28" s="32" t="inlineStr">
         <is>
           <t>Capsule</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="I28" s="32" t="inlineStr">
         <is>
           <t>胶囊</t>
         </is>
       </c>
-      <c r="J28" t="n">
+      <c r="J28" s="32" t="n">
         <v>4</v>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="K28" s="32" t="inlineStr">
         <is>
           <t>胶囊线段</t>
         </is>
@@ -3883,102 +3879,166 @@
     </row>
     <row r="29"/>
     <row r="30">
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="32" t="inlineStr">
         <is>
           <t>Battle.BuffStackMode</t>
         </is>
       </c>
-      <c r="C30" t="b">
+      <c r="C30" s="32" t="b">
         <v>0</v>
       </c>
-      <c r="D30" t="b">
+      <c r="D30" s="32" t="b">
         <v>1</v>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F30" s="32" t="inlineStr">
         <is>
           <t>Buff叠加规则</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H30" s="32" t="inlineStr">
         <is>
           <t>Refresh</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="I30" s="32" t="inlineStr">
         <is>
           <t>刷新</t>
         </is>
       </c>
-      <c r="J30" t="n">
+      <c r="J30" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="K30" s="32" t="inlineStr">
         <is>
           <t>刷新持续时间</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="H31" t="inlineStr">
+      <c r="H31" s="32" t="inlineStr">
         <is>
           <t>Stack</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="I31" s="32" t="inlineStr">
         <is>
           <t>叠层</t>
         </is>
       </c>
-      <c r="J31" t="n">
+      <c r="J31" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="K31" s="32" t="inlineStr">
         <is>
           <t>只增加层数</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="H32" t="inlineStr">
+      <c r="H32" s="32" t="inlineStr">
         <is>
           <t>RefreshAndStack</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="I32" s="32" t="inlineStr">
         <is>
           <t>刷新并叠层</t>
         </is>
       </c>
-      <c r="J32" t="n">
+      <c r="J32" s="32" t="n">
         <v>3</v>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="K32" s="32" t="inlineStr">
         <is>
           <t>刷新时间并增加层数</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="H33" t="inlineStr">
+      <c r="H33" s="32" t="inlineStr">
         <is>
           <t>Replace</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="I33" s="32" t="inlineStr">
         <is>
           <t>替换</t>
         </is>
       </c>
-      <c r="J33" t="n">
+      <c r="J33" s="32" t="n">
         <v>4</v>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="K33" s="32" t="inlineStr">
         <is>
           <t>替换旧Buff</t>
         </is>
       </c>
     </row>
     <row r="34"/>
+    <row r="35">
+      <c r="B35" s="32" t="inlineStr">
+        <is>
+          <t>Battle.QueryQuality</t>
+        </is>
+      </c>
+      <c r="C35" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="D35" s="32" t="b">
+        <v>1</v>
+      </c>
+      <c r="F35" s="32" t="inlineStr">
+        <is>
+          <t>Query quality</t>
+        </is>
+      </c>
+      <c r="H35" s="32" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I35" s="32" t="n"/>
+      <c r="J35" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" s="32" t="inlineStr">
+        <is>
+          <t>Current position only</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="H36" s="32" t="inlineStr">
+        <is>
+          <t>Mid</t>
+        </is>
+      </c>
+      <c r="I36" s="32" t="n"/>
+      <c r="J36" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="K36" s="32" t="inlineStr">
+        <is>
+          <t>Full path query</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="H37" s="32" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I37" s="32" t="n"/>
+      <c r="J37" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="K37" s="32" t="inlineStr">
+        <is>
+          <t>Full path and nearest hit</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>

--- a/Excels/Excels/__enums__.xlsx
+++ b/Excels/Excels/__enums__.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="245">
   <si>
     <t xml:space="preserve">##var</t>
   </si>
@@ -482,6 +482,12 @@
   </si>
   <si>
     <t xml:space="preserve">霸体</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intercept</t>
+  </si>
+  <si>
+    <t xml:space="preserve">拦截数</t>
   </si>
   <si>
     <t xml:space="preserve">Attr.GroupType</t>
@@ -895,109 +901,101 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="24">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1355,11 +1353,11 @@
       <c r="B4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="8" t="b">
+      <c r="C4" s="1" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="D4" s="8" t="b">
+      <c r="D4" s="1" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -1378,14 +1376,14 @@
     </row>
     <row r="5" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="6" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H6" s="9" t="s">
+      <c r="H6" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="I6" s="10"/>
-      <c r="J6" s="10" t="n">
+      <c r="I6" s="9"/>
+      <c r="J6" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="K6" s="10" t="s">
+      <c r="K6" s="9" t="s">
         <v>24</v>
       </c>
     </row>
@@ -1435,14 +1433,14 @@
     </row>
     <row r="11" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="12" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H12" s="9" t="s">
+      <c r="H12" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="I12" s="10"/>
-      <c r="J12" s="10" t="n">
+      <c r="I12" s="9"/>
+      <c r="J12" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="K12" s="10" t="s">
+      <c r="K12" s="9" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1481,19 +1479,19 @@
     </row>
     <row r="16" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="17" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H17" s="9" t="s">
+      <c r="H17" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="I17" s="10"/>
-      <c r="J17" s="10" t="n">
+      <c r="I17" s="9"/>
+      <c r="J17" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="K17" s="10" t="s">
+      <c r="K17" s="9" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H18" s="11" t="s">
+      <c r="H18" s="10" t="s">
         <v>43</v>
       </c>
       <c r="J18" s="3" t="n">
@@ -1504,7 +1502,7 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H19" s="11" t="s">
+      <c r="H19" s="10" t="s">
         <v>45</v>
       </c>
       <c r="J19" s="3" t="n">
@@ -1515,7 +1513,7 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H20" s="11" t="s">
+      <c r="H20" s="10" t="s">
         <v>47</v>
       </c>
       <c r="J20" s="3" t="n">
@@ -1537,7 +1535,7 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H22" s="11" t="s">
+      <c r="H22" s="10" t="s">
         <v>51</v>
       </c>
       <c r="J22" s="3" t="n">
@@ -1548,7 +1546,7 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H23" s="11" t="s">
+      <c r="H23" s="10" t="s">
         <v>53</v>
       </c>
       <c r="J23" s="3" t="n">
@@ -1559,10 +1557,10 @@
       </c>
     </row>
     <row r="24" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H24" s="11"/>
+      <c r="H24" s="10"/>
     </row>
     <row r="25" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H25" s="11" t="s">
+      <c r="H25" s="10" t="s">
         <v>55</v>
       </c>
       <c r="J25" s="3" t="n">
@@ -1573,7 +1571,7 @@
       </c>
     </row>
     <row r="26" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H26" s="11" t="s">
+      <c r="H26" s="10" t="s">
         <v>57</v>
       </c>
       <c r="J26" s="3" t="n">
@@ -1584,7 +1582,7 @@
       </c>
     </row>
     <row r="27" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H27" s="11" t="s">
+      <c r="H27" s="10" t="s">
         <v>59</v>
       </c>
       <c r="J27" s="3" t="n">
@@ -1595,10 +1593,10 @@
       </c>
     </row>
     <row r="28" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H28" s="11"/>
+      <c r="H28" s="10"/>
     </row>
     <row r="29" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H29" s="11" t="s">
+      <c r="H29" s="10" t="s">
         <v>61</v>
       </c>
       <c r="J29" s="3" t="n">
@@ -1665,7 +1663,7 @@
     </row>
     <row r="35" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="36" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H36" s="11" t="s">
+      <c r="H36" s="10" t="s">
         <v>73</v>
       </c>
       <c r="J36" s="3" t="n">
@@ -1676,7 +1674,7 @@
       </c>
     </row>
     <row r="37" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H37" s="11" t="s">
+      <c r="H37" s="10" t="s">
         <v>75</v>
       </c>
       <c r="J37" s="3" t="n">
@@ -1687,7 +1685,7 @@
       </c>
     </row>
     <row r="38" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H38" s="11" t="s">
+      <c r="H38" s="10" t="s">
         <v>77</v>
       </c>
       <c r="J38" s="3" t="n">
@@ -1698,10 +1696,10 @@
       </c>
     </row>
     <row r="39" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H39" s="11"/>
+      <c r="H39" s="10"/>
     </row>
     <row r="40" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H40" s="11" t="s">
+      <c r="H40" s="10" t="s">
         <v>79</v>
       </c>
       <c r="J40" s="3" t="n">
@@ -1712,7 +1710,7 @@
       </c>
     </row>
     <row r="42" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H42" s="11" t="s">
+      <c r="H42" s="10" t="s">
         <v>81</v>
       </c>
       <c r="J42" s="3" t="n">
@@ -1723,10 +1721,10 @@
       </c>
     </row>
     <row r="43" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H43" s="11"/>
+      <c r="H43" s="10"/>
     </row>
     <row r="44" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H44" s="11" t="s">
+      <c r="H44" s="10" t="s">
         <v>83</v>
       </c>
       <c r="J44" s="3" t="n">
@@ -1737,7 +1735,7 @@
       </c>
     </row>
     <row r="45" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H45" s="11" t="s">
+      <c r="H45" s="10" t="s">
         <v>85</v>
       </c>
       <c r="J45" s="3" t="n">
@@ -1748,10 +1746,10 @@
       </c>
     </row>
     <row r="46" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H46" s="11"/>
+      <c r="H46" s="10"/>
     </row>
     <row r="47" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H47" s="11" t="s">
+      <c r="H47" s="10" t="s">
         <v>87</v>
       </c>
       <c r="J47" s="3" t="n">
@@ -1806,14 +1804,14 @@
       </c>
     </row>
     <row r="53" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H53" s="9" t="s">
+      <c r="H53" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="I53" s="10"/>
-      <c r="J53" s="10" t="n">
+      <c r="I53" s="9"/>
+      <c r="J53" s="9" t="n">
         <v>10000</v>
       </c>
-      <c r="K53" s="10" t="s">
+      <c r="K53" s="9" t="s">
         <v>98</v>
       </c>
     </row>
@@ -1862,8 +1860,8 @@
   <dimension ref="A1:L48"/>
   <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="12" width="17.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="12" width="51.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="11" width="17.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="11" width="51.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="13"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="10" min="9" style="1" width="9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="9.25"/>
@@ -1956,10 +1954,10 @@
       <c r="L3" s="4"/>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="11" t="s">
         <v>104</v>
       </c>
       <c r="H4" s="1" t="s">
@@ -2007,10 +2005,10 @@
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="F9" s="12" t="s">
+      <c r="F9" s="11" t="s">
         <v>114</v>
       </c>
       <c r="H9" s="1" t="s">
@@ -2024,10 +2022,10 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="F11" s="12" t="s">
+      <c r="F11" s="11" t="s">
         <v>117</v>
       </c>
       <c r="H11" s="1" t="s">
@@ -2052,12 +2050,12 @@
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J47" s="13"/>
-      <c r="K47" s="14"/>
+      <c r="J47" s="12"/>
+      <c r="K47" s="13"/>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J48" s="13"/>
-      <c r="K48" s="14"/>
+      <c r="J48" s="12"/>
+      <c r="K48" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2081,12 +2079,12 @@
   <dimension ref="A1:L62"/>
   <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="12.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="12" width="36.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="12" width="29.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="12" width="16.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="12" width="13.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="12" width="19.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="12" width="23.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="11" width="36.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="11" width="29.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="11" width="16.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="11" width="13.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="11" width="19.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="11" width="23.75"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2111,13 +2109,13 @@
       <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="H1" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
@@ -2129,7 +2127,7 @@
       <c r="E2" s="4"/>
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
-      <c r="H2" s="15" t="s">
+      <c r="H2" s="14" t="s">
         <v>8</v>
       </c>
       <c r="I2" s="4" t="s">
@@ -2161,7 +2159,7 @@
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
       <c r="G3" s="4"/>
-      <c r="H3" s="15" t="s">
+      <c r="H3" s="14" t="s">
         <v>15</v>
       </c>
       <c r="I3" s="4" t="s">
@@ -2180,11 +2178,11 @@
       <c r="B4" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C4" s="8" t="b">
+      <c r="C4" s="1" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="D4" s="8" t="b">
+      <c r="D4" s="1" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -2193,7 +2191,7 @@
         <v>122</v>
       </c>
       <c r="G4" s="1"/>
-      <c r="H4" s="16" t="s">
+      <c r="H4" s="15" t="s">
         <v>123</v>
       </c>
       <c r="I4" s="1" t="s">
@@ -2213,7 +2211,7 @@
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
-      <c r="H5" s="16" t="s">
+      <c r="H5" s="15" t="s">
         <v>125</v>
       </c>
       <c r="I5" s="1" t="s">
@@ -2233,7 +2231,7 @@
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
-      <c r="H6" s="16" t="s">
+      <c r="H6" s="15" t="s">
         <v>127</v>
       </c>
       <c r="I6" s="1" t="s">
@@ -2253,7 +2251,7 @@
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
-      <c r="H7" s="16" t="s">
+      <c r="H7" s="15" t="s">
         <v>129</v>
       </c>
       <c r="I7" s="1" t="s">
@@ -2273,7 +2271,7 @@
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
-      <c r="H8" s="16" t="s">
+      <c r="H8" s="15" t="s">
         <v>131</v>
       </c>
       <c r="I8" s="1" t="s">
@@ -2293,7 +2291,7 @@
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
-      <c r="H9" s="16" t="s">
+      <c r="H9" s="15" t="s">
         <v>133</v>
       </c>
       <c r="I9" s="1" t="s">
@@ -2313,7 +2311,7 @@
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
-      <c r="H10" s="16"/>
+      <c r="H10" s="15"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
@@ -2321,14 +2319,14 @@
     </row>
     <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1"/>
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="16" t="s">
         <v>135</v>
       </c>
-      <c r="C11" s="8" t="b">
+      <c r="C11" s="1" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="D11" s="8" t="b">
+      <c r="D11" s="1" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -2337,7 +2335,7 @@
         <v>136</v>
       </c>
       <c r="G11" s="1"/>
-      <c r="H11" s="12" t="s">
+      <c r="H11" s="11" t="s">
         <v>137</v>
       </c>
       <c r="I11" s="1" t="s">
@@ -2357,7 +2355,7 @@
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
-      <c r="H12" s="12" t="s">
+      <c r="H12" s="11" t="s">
         <v>139</v>
       </c>
       <c r="I12" s="1" t="s">
@@ -2377,7 +2375,7 @@
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
-      <c r="H13" s="16" t="s">
+      <c r="H13" s="15" t="s">
         <v>141</v>
       </c>
       <c r="I13" s="1" t="s">
@@ -2397,7 +2395,7 @@
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
-      <c r="H14" s="12" t="s">
+      <c r="H14" s="11" t="s">
         <v>143</v>
       </c>
       <c r="I14" s="1" t="s">
@@ -2417,7 +2415,7 @@
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
-      <c r="H15" s="16" t="s">
+      <c r="H15" s="15" t="s">
         <v>145</v>
       </c>
       <c r="I15" s="1" t="s">
@@ -2437,7 +2435,7 @@
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
-      <c r="H16" s="16" t="s">
+      <c r="H16" s="15" t="s">
         <v>147</v>
       </c>
       <c r="I16" s="1" t="s">
@@ -2457,13 +2455,13 @@
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
-      <c r="H17" s="16" t="s">
+      <c r="H17" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="I17" s="18" t="s">
+      <c r="I17" s="17" t="s">
         <v>150</v>
       </c>
-      <c r="J17" s="18" t="n">
+      <c r="J17" s="17" t="n">
         <v>105</v>
       </c>
       <c r="K17" s="1"/>
@@ -2477,7 +2475,7 @@
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
-      <c r="H18" s="16" t="s">
+      <c r="H18" s="15" t="s">
         <v>151</v>
       </c>
       <c r="I18" s="1" t="s">
@@ -2497,8 +2495,15 @@
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
+      <c r="H19" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="J19" s="1" t="n">
+        <v>202</v>
+      </c>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
     </row>
@@ -2510,7 +2515,7 @@
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
-      <c r="H20" s="16"/>
+      <c r="H20" s="15"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
@@ -2524,9 +2529,9 @@
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
-      <c r="H21" s="16"/>
-      <c r="I21" s="18"/>
-      <c r="J21" s="18"/>
+      <c r="H21" s="15"/>
+      <c r="I21" s="17"/>
+      <c r="J21" s="17"/>
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
     </row>
@@ -2536,9 +2541,9 @@
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
-      <c r="F22" s="16"/>
+      <c r="F22" s="15"/>
       <c r="G22" s="1"/>
-      <c r="H22" s="16"/>
+      <c r="H22" s="15"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
@@ -2550,9 +2555,9 @@
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
-      <c r="F23" s="16"/>
+      <c r="F23" s="15"/>
       <c r="G23" s="1"/>
-      <c r="H23" s="16"/>
+      <c r="H23" s="15"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
@@ -2564,9 +2569,9 @@
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
-      <c r="F24" s="16"/>
+      <c r="F24" s="15"/>
       <c r="G24" s="1"/>
-      <c r="H24" s="16"/>
+      <c r="H24" s="15"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
@@ -2578,9 +2583,9 @@
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
-      <c r="F25" s="16"/>
+      <c r="F25" s="15"/>
       <c r="G25" s="1"/>
-      <c r="H25" s="16"/>
+      <c r="H25" s="15"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
@@ -2592,9 +2597,9 @@
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
-      <c r="F26" s="16"/>
+      <c r="F26" s="15"/>
       <c r="G26" s="1"/>
-      <c r="H26" s="16"/>
+      <c r="H26" s="15"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
@@ -2606,9 +2611,9 @@
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
-      <c r="F27" s="16"/>
+      <c r="F27" s="15"/>
       <c r="G27" s="1"/>
-      <c r="H27" s="16"/>
+      <c r="H27" s="15"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
       <c r="K27" s="1"/>
@@ -2620,9 +2625,9 @@
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
-      <c r="F28" s="16"/>
+      <c r="F28" s="15"/>
       <c r="G28" s="1"/>
-      <c r="H28" s="16"/>
+      <c r="H28" s="15"/>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
@@ -2634,9 +2639,9 @@
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
-      <c r="F29" s="16"/>
+      <c r="F29" s="15"/>
       <c r="G29" s="1"/>
-      <c r="H29" s="16"/>
+      <c r="H29" s="15"/>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
@@ -2648,9 +2653,9 @@
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
-      <c r="F30" s="16"/>
+      <c r="F30" s="15"/>
       <c r="G30" s="1"/>
-      <c r="H30" s="16"/>
+      <c r="H30" s="15"/>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
@@ -2662,9 +2667,9 @@
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
-      <c r="F31" s="16"/>
+      <c r="F31" s="15"/>
       <c r="G31" s="1"/>
-      <c r="H31" s="16"/>
+      <c r="H31" s="15"/>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
@@ -2676,9 +2681,9 @@
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
-      <c r="F32" s="16"/>
+      <c r="F32" s="15"/>
       <c r="G32" s="1"/>
-      <c r="H32" s="16"/>
+      <c r="H32" s="15"/>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
       <c r="K32" s="1"/>
@@ -2690,11 +2695,11 @@
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
-      <c r="F33" s="16"/>
+      <c r="F33" s="15"/>
       <c r="G33" s="1"/>
-      <c r="H33" s="16"/>
-      <c r="I33" s="18"/>
-      <c r="J33" s="18"/>
+      <c r="H33" s="15"/>
+      <c r="I33" s="17"/>
+      <c r="J33" s="17"/>
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
     </row>
@@ -2706,7 +2711,7 @@
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
-      <c r="H34" s="16"/>
+      <c r="H34" s="15"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
@@ -2720,7 +2725,7 @@
       <c r="E35" s="1"/>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
-      <c r="H35" s="16"/>
+      <c r="H35" s="15"/>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
@@ -2734,7 +2739,7 @@
       <c r="E36" s="1"/>
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
-      <c r="H36" s="16"/>
+      <c r="H36" s="15"/>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
@@ -2748,7 +2753,7 @@
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
-      <c r="H37" s="16"/>
+      <c r="H37" s="15"/>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
@@ -2762,7 +2767,7 @@
       <c r="E38" s="1"/>
       <c r="F38" s="1"/>
       <c r="G38" s="1"/>
-      <c r="H38" s="16"/>
+      <c r="H38" s="15"/>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
       <c r="K38" s="1"/>
@@ -2776,7 +2781,7 @@
       <c r="E39" s="1"/>
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
-      <c r="H39" s="16"/>
+      <c r="H39" s="15"/>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
       <c r="K39" s="1"/>
@@ -2790,7 +2795,7 @@
       <c r="E40" s="1"/>
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
-      <c r="H40" s="16"/>
+      <c r="H40" s="15"/>
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
@@ -2804,7 +2809,7 @@
       <c r="E41" s="1"/>
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
-      <c r="H41" s="16"/>
+      <c r="H41" s="15"/>
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
       <c r="K41" s="1"/>
@@ -2818,7 +2823,7 @@
       <c r="E42" s="1"/>
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
-      <c r="H42" s="16"/>
+      <c r="H42" s="15"/>
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
       <c r="K42" s="1"/>
@@ -2832,7 +2837,7 @@
       <c r="E43" s="1"/>
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
-      <c r="H43" s="16"/>
+      <c r="H43" s="15"/>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
       <c r="K43" s="1"/>
@@ -2846,7 +2851,7 @@
       <c r="E44" s="1"/>
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
-      <c r="H44" s="16"/>
+      <c r="H44" s="15"/>
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
       <c r="K44" s="1"/>
@@ -2860,7 +2865,7 @@
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>
-      <c r="H45" s="16"/>
+      <c r="H45" s="15"/>
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
       <c r="K45" s="1"/>
@@ -2874,7 +2879,7 @@
       <c r="E46" s="1"/>
       <c r="F46" s="1"/>
       <c r="G46" s="1"/>
-      <c r="H46" s="16"/>
+      <c r="H46" s="15"/>
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
       <c r="K46" s="1"/>
@@ -2888,7 +2893,7 @@
       <c r="E47" s="1"/>
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
-      <c r="H47" s="16"/>
+      <c r="H47" s="15"/>
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
       <c r="K47" s="1"/>
@@ -2902,7 +2907,7 @@
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
       <c r="G48" s="1"/>
-      <c r="H48" s="16"/>
+      <c r="H48" s="15"/>
       <c r="I48" s="1"/>
       <c r="J48" s="1"/>
       <c r="K48" s="1"/>
@@ -2916,7 +2921,7 @@
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
-      <c r="H49" s="16"/>
+      <c r="H49" s="15"/>
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
       <c r="K49" s="1"/>
@@ -2930,7 +2935,7 @@
       <c r="E50" s="1"/>
       <c r="F50" s="1"/>
       <c r="G50" s="1"/>
-      <c r="H50" s="16"/>
+      <c r="H50" s="15"/>
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
       <c r="K50" s="1"/>
@@ -2944,7 +2949,7 @@
       <c r="E51" s="1"/>
       <c r="F51" s="1"/>
       <c r="G51" s="1"/>
-      <c r="H51" s="16"/>
+      <c r="H51" s="15"/>
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
       <c r="K51" s="1"/>
@@ -2958,7 +2963,7 @@
       <c r="E52" s="1"/>
       <c r="F52" s="1"/>
       <c r="G52" s="1"/>
-      <c r="H52" s="16"/>
+      <c r="H52" s="15"/>
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
@@ -2972,7 +2977,7 @@
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
       <c r="G53" s="1"/>
-      <c r="H53" s="16"/>
+      <c r="H53" s="15"/>
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
       <c r="K53" s="1"/>
@@ -2986,7 +2991,7 @@
       <c r="E54" s="1"/>
       <c r="F54" s="1"/>
       <c r="G54" s="1"/>
-      <c r="H54" s="19"/>
+      <c r="H54" s="18"/>
       <c r="I54" s="1"/>
       <c r="J54" s="1"/>
       <c r="K54" s="1"/>
@@ -3000,7 +3005,7 @@
       <c r="E55" s="1"/>
       <c r="F55" s="1"/>
       <c r="G55" s="1"/>
-      <c r="H55" s="19"/>
+      <c r="H55" s="18"/>
       <c r="I55" s="1"/>
       <c r="J55" s="1"/>
       <c r="K55" s="1"/>
@@ -3009,82 +3014,82 @@
     <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="57" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B57" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="C57" s="8" t="b">
+        <v>155</v>
+      </c>
+      <c r="C57" s="1" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="D57" s="8" t="b">
+      <c r="D57" s="1" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="E57" s="1"/>
       <c r="F57" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="H57" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="H57" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="I57" s="12" t="s">
+      <c r="I57" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="J57" s="12" t="n">
+      <c r="J57" s="11" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H58" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="I58" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="J58" s="12" t="n">
+      <c r="H58" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="I58" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="J58" s="11" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H59" s="12" t="s">
-        <v>157</v>
-      </c>
-      <c r="I59" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="J59" s="12" t="n">
+      <c r="H59" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="I59" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="J59" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H60" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="I60" s="12" t="s">
-        <v>160</v>
-      </c>
-      <c r="J60" s="12" t="n">
+      <c r="H60" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="I60" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="J60" s="11" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H61" s="12" t="s">
-        <v>161</v>
-      </c>
-      <c r="I61" s="12" t="s">
-        <v>162</v>
-      </c>
-      <c r="J61" s="12" t="n">
+      <c r="H61" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="I61" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="J61" s="11" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H62" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="I62" s="12" t="s">
-        <v>164</v>
-      </c>
-      <c r="J62" s="12" t="n">
+      <c r="H62" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="I62" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="J62" s="11" t="n">
         <v>5</v>
       </c>
     </row>
@@ -3110,583 +3115,583 @@
   <dimension ref="A1:L37"/>
   <sheetFormatPr defaultColWidth="8.51953125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="20" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="20" width="25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="20" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="20" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="20" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="20" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="20" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="19" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="19" width="25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="19" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="19" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="19" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="19" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="19" width="10"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="B1" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="C1" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="D1" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="21" t="s">
+      <c r="E1" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="21" t="s">
+      <c r="F1" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="21" t="s">
+      <c r="G1" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="22" t="s">
+      <c r="H1" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="22"/>
-      <c r="J1" s="22"/>
-      <c r="K1" s="22"/>
-      <c r="L1" s="22"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="21"/>
+      <c r="L1" s="21"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
-      <c r="G2" s="23"/>
-      <c r="H2" s="23" t="s">
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="23" t="s">
+      <c r="I2" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="23" t="s">
+      <c r="J2" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="23" t="s">
+      <c r="K2" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="L2" s="23" t="s">
+      <c r="L2" s="22" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="24" t="s">
-        <v>165</v>
-      </c>
-      <c r="D3" s="24" t="s">
+      <c r="C3" s="23" t="s">
+        <v>167</v>
+      </c>
+      <c r="D3" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="24" t="s">
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="23"/>
+      <c r="H3" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="24" t="s">
+      <c r="I3" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="J3" s="24" t="s">
+      <c r="J3" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="24" t="s">
+      <c r="K3" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="L3" s="24"/>
+      <c r="L3" s="23"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="12" t="s">
-        <v>166</v>
-      </c>
-      <c r="C4" s="25" t="b">
+      <c r="B4" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="C4" s="11" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="D4" s="25" t="b">
+      <c r="D4" s="11" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="F4" s="12" t="s">
-        <v>167</v>
-      </c>
-      <c r="H4" s="12" t="s">
+      <c r="F4" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="H4" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="I4" s="12" t="s">
+      <c r="I4" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="J4" s="12" t="n">
+      <c r="J4" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="K4" s="12" t="s">
+      <c r="K4" s="11" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H5" s="12" t="s">
-        <v>168</v>
-      </c>
-      <c r="I5" s="12" t="s">
-        <v>169</v>
-      </c>
-      <c r="J5" s="12" t="n">
+      <c r="H5" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="J5" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="K5" s="12" t="s">
-        <v>170</v>
+      <c r="K5" s="11" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H6" s="12" t="s">
-        <v>171</v>
-      </c>
-      <c r="I6" s="12" t="s">
-        <v>172</v>
-      </c>
-      <c r="J6" s="12" t="n">
+      <c r="H6" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="J6" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="K6" s="12" t="s">
-        <v>173</v>
+      <c r="K6" s="11" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H7" s="12" t="s">
-        <v>174</v>
-      </c>
-      <c r="I7" s="12" t="s">
-        <v>175</v>
-      </c>
-      <c r="J7" s="12" t="n">
+      <c r="H7" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="J7" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="K7" s="12" t="s">
-        <v>175</v>
+      <c r="K7" s="11" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H8" s="12" t="s">
-        <v>176</v>
-      </c>
-      <c r="I8" s="12" t="s">
-        <v>177</v>
-      </c>
-      <c r="J8" s="12" t="n">
+      <c r="H8" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="J8" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="K8" s="12" t="s">
-        <v>178</v>
+      <c r="K8" s="11" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="12" t="s">
-        <v>179</v>
-      </c>
-      <c r="C10" s="25" t="b">
+      <c r="B10" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="C10" s="11" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="D10" s="25" t="b">
+      <c r="D10" s="11" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="F10" s="12" t="s">
-        <v>180</v>
-      </c>
-      <c r="H10" s="12" t="s">
+      <c r="F10" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="H10" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="I10" s="12" t="s">
+      <c r="I10" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="J10" s="12" t="n">
+      <c r="J10" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="K10" s="12" t="s">
+      <c r="K10" s="11" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H11" s="12" t="s">
-        <v>181</v>
-      </c>
-      <c r="I11" s="12" t="s">
-        <v>182</v>
-      </c>
-      <c r="J11" s="12" t="n">
+      <c r="H11" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="I11" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="J11" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="K11" s="12" t="s">
-        <v>182</v>
+      <c r="K11" s="11" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H12" s="12" t="s">
-        <v>183</v>
-      </c>
-      <c r="I12" s="12" t="s">
-        <v>184</v>
-      </c>
-      <c r="J12" s="12" t="n">
+      <c r="H12" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="I12" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="J12" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="K12" s="12" t="s">
-        <v>184</v>
+      <c r="K12" s="11" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H13" s="12" t="s">
-        <v>185</v>
-      </c>
-      <c r="I13" s="12" t="s">
-        <v>186</v>
-      </c>
-      <c r="J13" s="12" t="n">
+      <c r="H13" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="I13" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="J13" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="K13" s="12" t="s">
-        <v>186</v>
+      <c r="K13" s="11" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H14" s="12" t="s">
-        <v>187</v>
-      </c>
-      <c r="I14" s="12" t="s">
-        <v>188</v>
-      </c>
-      <c r="J14" s="12" t="n">
+      <c r="H14" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="I14" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="J14" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="K14" s="12" t="s">
-        <v>189</v>
+      <c r="K14" s="11" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H15" s="12" t="s">
-        <v>190</v>
-      </c>
-      <c r="I15" s="12" t="s">
-        <v>191</v>
-      </c>
-      <c r="J15" s="12" t="n">
+      <c r="H15" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="I15" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="J15" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="K15" s="12" t="s">
-        <v>192</v>
+      <c r="K15" s="11" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="12" t="s">
-        <v>193</v>
-      </c>
-      <c r="C17" s="25" t="b">
+      <c r="B17" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C17" s="11" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="D17" s="25" t="b">
+      <c r="D17" s="11" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="F17" s="12" t="s">
-        <v>194</v>
-      </c>
-      <c r="H17" s="12" t="s">
+      <c r="F17" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="H17" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="I17" s="12" t="s">
+      <c r="I17" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="J17" s="12" t="n">
+      <c r="J17" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="K17" s="12" t="s">
+      <c r="K17" s="11" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H18" s="12" t="s">
-        <v>195</v>
-      </c>
-      <c r="I18" s="12" t="s">
-        <v>196</v>
-      </c>
-      <c r="J18" s="12" t="n">
+      <c r="H18" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="I18" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="J18" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="K18" s="12" t="s">
-        <v>197</v>
+      <c r="K18" s="11" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H19" s="12" t="s">
-        <v>198</v>
-      </c>
-      <c r="I19" s="12" t="s">
-        <v>199</v>
-      </c>
-      <c r="J19" s="12" t="n">
+      <c r="H19" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="I19" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="J19" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="K19" s="12" t="s">
-        <v>200</v>
+      <c r="K19" s="11" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H20" s="12" t="s">
-        <v>201</v>
-      </c>
-      <c r="I20" s="12" t="s">
-        <v>202</v>
-      </c>
-      <c r="J20" s="12" t="n">
+      <c r="H20" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="I20" s="11" t="s">
+        <v>204</v>
+      </c>
+      <c r="J20" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="K20" s="12" t="s">
-        <v>203</v>
+      <c r="K20" s="11" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H21" s="12" t="s">
-        <v>204</v>
-      </c>
-      <c r="I21" s="12" t="s">
-        <v>205</v>
-      </c>
-      <c r="J21" s="12" t="n">
+      <c r="H21" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="I21" s="11" t="s">
+        <v>207</v>
+      </c>
+      <c r="J21" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="K21" s="12" t="s">
-        <v>206</v>
+      <c r="K21" s="11" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H22" s="12" t="s">
-        <v>207</v>
-      </c>
-      <c r="I22" s="12" t="s">
-        <v>208</v>
-      </c>
-      <c r="J22" s="12" t="n">
+      <c r="H22" s="11" t="s">
+        <v>209</v>
+      </c>
+      <c r="I22" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="J22" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="K22" s="12" t="s">
-        <v>209</v>
+      <c r="K22" s="11" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="12" t="s">
-        <v>210</v>
-      </c>
-      <c r="C24" s="25" t="b">
+      <c r="B24" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="C24" s="11" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="D24" s="25" t="b">
+      <c r="D24" s="11" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="F24" s="12" t="s">
-        <v>211</v>
-      </c>
-      <c r="H24" s="12" t="s">
+      <c r="F24" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="H24" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="I24" s="12" t="s">
+      <c r="I24" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="J24" s="12" t="n">
+      <c r="J24" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="K24" s="12" t="s">
+      <c r="K24" s="11" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H25" s="12" t="s">
-        <v>212</v>
-      </c>
-      <c r="I25" s="12" t="s">
-        <v>213</v>
-      </c>
-      <c r="J25" s="12" t="n">
+      <c r="H25" s="11" t="s">
+        <v>214</v>
+      </c>
+      <c r="I25" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="J25" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="K25" s="12" t="s">
-        <v>213</v>
+      <c r="K25" s="11" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H26" s="12" t="s">
-        <v>214</v>
-      </c>
-      <c r="I26" s="12" t="s">
-        <v>215</v>
-      </c>
-      <c r="J26" s="12" t="n">
+      <c r="H26" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="I26" s="11" t="s">
+        <v>217</v>
+      </c>
+      <c r="J26" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="K26" s="12" t="s">
-        <v>215</v>
+      <c r="K26" s="11" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H27" s="12" t="s">
-        <v>216</v>
-      </c>
-      <c r="I27" s="12" t="s">
-        <v>217</v>
-      </c>
-      <c r="J27" s="12" t="n">
+      <c r="H27" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="I27" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="J27" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="K27" s="12" t="s">
-        <v>217</v>
+      <c r="K27" s="11" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H28" s="12" t="s">
-        <v>218</v>
-      </c>
-      <c r="I28" s="12" t="s">
-        <v>219</v>
-      </c>
-      <c r="J28" s="12" t="n">
+      <c r="H28" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="I28" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="J28" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="K28" s="12" t="s">
-        <v>220</v>
+      <c r="K28" s="11" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="12" t="s">
-        <v>221</v>
-      </c>
-      <c r="C30" s="25" t="b">
+      <c r="B30" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="C30" s="11" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="D30" s="25" t="b">
+      <c r="D30" s="11" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="F30" s="12" t="s">
-        <v>222</v>
-      </c>
-      <c r="H30" s="12" t="s">
-        <v>223</v>
-      </c>
-      <c r="I30" s="12" t="s">
+      <c r="F30" s="11" t="s">
         <v>224</v>
       </c>
-      <c r="J30" s="12" t="n">
+      <c r="H30" s="11" t="s">
+        <v>225</v>
+      </c>
+      <c r="I30" s="11" t="s">
+        <v>226</v>
+      </c>
+      <c r="J30" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="K30" s="12" t="s">
-        <v>225</v>
+      <c r="K30" s="11" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H31" s="12" t="s">
-        <v>226</v>
-      </c>
-      <c r="I31" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="J31" s="12" t="n">
+      <c r="H31" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="I31" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="J31" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="K31" s="12" t="s">
-        <v>228</v>
+      <c r="K31" s="11" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H32" s="12" t="s">
-        <v>229</v>
-      </c>
-      <c r="I32" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="J32" s="12" t="n">
+      <c r="H32" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="I32" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="J32" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="K32" s="12" t="s">
-        <v>231</v>
+      <c r="K32" s="11" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H33" s="12" t="s">
-        <v>232</v>
-      </c>
-      <c r="I33" s="12" t="s">
-        <v>233</v>
-      </c>
-      <c r="J33" s="12" t="n">
+      <c r="H33" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="I33" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="J33" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="K33" s="12" t="s">
-        <v>234</v>
+      <c r="K33" s="11" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="12" t="s">
-        <v>235</v>
-      </c>
-      <c r="C35" s="25" t="b">
+      <c r="B35" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="C35" s="11" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="D35" s="25" t="b">
+      <c r="D35" s="11" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="F35" s="12" t="s">
-        <v>236</v>
-      </c>
-      <c r="H35" s="12" t="s">
-        <v>237</v>
-      </c>
-      <c r="I35" s="12"/>
-      <c r="J35" s="12" t="n">
+      <c r="F35" s="11" t="s">
+        <v>238</v>
+      </c>
+      <c r="H35" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="I35" s="11"/>
+      <c r="J35" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="K35" s="12" t="s">
-        <v>238</v>
+      <c r="K35" s="11" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H36" s="12" t="s">
-        <v>239</v>
-      </c>
-      <c r="I36" s="12"/>
-      <c r="J36" s="12" t="n">
+      <c r="H36" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="I36" s="11"/>
+      <c r="J36" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="K36" s="12" t="s">
-        <v>240</v>
+      <c r="K36" s="11" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H37" s="12" t="s">
-        <v>241</v>
-      </c>
-      <c r="I37" s="12"/>
-      <c r="J37" s="12" t="n">
+      <c r="H37" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="I37" s="11"/>
+      <c r="J37" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="K37" s="12" t="s">
-        <v>242</v>
+      <c r="K37" s="11" t="s">
+        <v>244</v>
       </c>
     </row>
   </sheetData>

--- a/Excels/Excels/__enums__.xlsx
+++ b/Excels/Excels/__enums__.xlsx
@@ -2747,7 +2747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:L65"/>
+  <dimension ref="A1:L66"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.51953125" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="10" customWidth="1" style="44" min="1" max="1"/>
@@ -3852,130 +3852,162 @@
     </row>
     <row r="57"/>
     <row r="58" ht="15" customHeight="1" s="26">
-      <c r="B58" s="36" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>Battle.SkillModifierType</t>
         </is>
       </c>
-      <c r="C58" s="36">
+      <c r="C58">
         <f>FALSE()</f>
         <v/>
       </c>
-      <c r="D58" s="36">
+      <c r="D58">
         <f>TRUE()</f>
         <v/>
       </c>
-      <c r="F58" s="36" t="inlineStr">
-        <is>
-          <t>技能强化类型</t>
-        </is>
-      </c>
-      <c r="H58" s="36" t="inlineStr">
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>??????</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="J58" s="36" t="n">
+      <c r="J58" t="n">
         <v>0</v>
       </c>
-      <c r="K58" s="36" t="inlineStr">
-        <is>
-          <t>无</t>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>?</t>
         </is>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1" s="26">
-      <c r="H59" s="36" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t>ProjectileNum</t>
         </is>
       </c>
-      <c r="J59" s="36" t="n">
+      <c r="J59" t="n">
         <v>1</v>
       </c>
-      <c r="K59" s="36" t="inlineStr">
-        <is>
-          <t>额外弹道数量</t>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>??????</t>
         </is>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1" s="26">
-      <c r="H60" s="36" t="inlineStr">
+      <c r="H60" t="inlineStr">
         <is>
           <t>AttackSpeed</t>
         </is>
       </c>
-      <c r="J60" s="36" t="n">
+      <c r="J60" t="n">
         <v>2</v>
       </c>
-      <c r="K60" s="36" t="inlineStr">
-        <is>
-          <t>攻击速度</t>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>????</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="H61" s="36" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t>CooldownReduction</t>
         </is>
       </c>
-      <c r="J61" s="36" t="n">
+      <c r="J61" t="n">
         <v>3</v>
       </c>
-      <c r="K61" s="36" t="inlineStr">
-        <is>
-          <t>冷却缩减</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="15" customHeight="1" s="26">
-      <c r="H62" s="36" t="inlineStr">
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>????</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="15" customHeight="1" s="26"/>
+    <row r="63" ht="15" customHeight="1" s="26">
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Battle.ProjectileModifierType</t>
+        </is>
+      </c>
+      <c r="C63">
+        <f>FALSE()</f>
+        <v/>
+      </c>
+      <c r="D63">
+        <f>TRUE()</f>
+        <v/>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>??????</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="15" customHeight="1" s="26">
+      <c r="H64" t="inlineStr">
         <is>
           <t>ReplaceProjectile</t>
         </is>
       </c>
-      <c r="J62" s="36" t="n">
-        <v>4</v>
-      </c>
-      <c r="K62" s="36" t="inlineStr">
-        <is>
-          <t>替换弹道效果</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="15" customHeight="1" s="26">
-      <c r="H63" s="36" t="inlineStr">
+      <c r="J64" t="n">
+        <v>1</v>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>??????</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="15" customHeight="1" s="26">
+      <c r="H65" t="inlineStr">
         <is>
           <t>ProjectilePierce</t>
         </is>
       </c>
-      <c r="J63" s="36" t="n">
-        <v>5</v>
-      </c>
-      <c r="K63" s="36" t="inlineStr">
-        <is>
-          <t>弹道穿透增量</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="15" customHeight="1" s="26">
-      <c r="H64" s="36" t="inlineStr">
+      <c r="J65" t="n">
+        <v>2</v>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>??????</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="15" customHeight="1" s="26">
+      <c r="H66" t="inlineStr">
         <is>
           <t>ProjectileHitArea</t>
         </is>
       </c>
-      <c r="J64" s="36" t="n">
-        <v>6</v>
-      </c>
-      <c r="K64" s="36" t="inlineStr">
-        <is>
-          <t>弹道命中范围</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="15" customHeight="1" s="26"/>
-    <row r="66" ht="15" customHeight="1" s="26"/>
+      <c r="J66" t="n">
+        <v>3</v>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>??????</t>
+        </is>
+      </c>
+    </row>
     <row r="67" ht="15" customHeight="1" s="26"/>
     <row r="68" ht="15" customHeight="1" s="26"/>
     <row r="70" ht="15" customHeight="1" s="26"/>

--- a/Excels/Excels/__enums__.xlsx
+++ b/Excels/Excels/__enums__.xlsx
@@ -2747,7 +2747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:L66"/>
+  <dimension ref="A1:L74"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.51953125" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="10" customWidth="1" style="44" min="1" max="1"/>
@@ -3758,262 +3758,380 @@
     </row>
     <row r="51"/>
     <row r="52" ht="15" customHeight="1" s="26">
-      <c r="B52" s="36" t="inlineStr">
-        <is>
-          <t>Battle.ModifierTargetType</t>
-        </is>
-      </c>
-      <c r="C52" s="36">
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Battle.ModifierSourceType</t>
+        </is>
+      </c>
+      <c r="C52">
         <f>FALSE()</f>
         <v/>
       </c>
-      <c r="D52" s="36">
+      <c r="D52">
         <f>TRUE()</f>
         <v/>
       </c>
-      <c r="F52" s="36" t="inlineStr">
-        <is>
-          <t>强化目标类型</t>
-        </is>
-      </c>
-      <c r="H52" s="36" t="inlineStr">
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>??????</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="J52" s="36" t="n">
+      <c r="J52" t="n">
         <v>0</v>
       </c>
-      <c r="K52" s="36" t="inlineStr">
-        <is>
-          <t>无</t>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>?</t>
         </is>
       </c>
     </row>
     <row r="53" ht="15" customHeight="1" s="26">
-      <c r="H53" s="36" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="J53" s="36" t="n">
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>RogueEnhancement</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
         <v>1</v>
       </c>
-      <c r="K53" s="36" t="inlineStr">
-        <is>
-          <t>单位强化</t>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>????</t>
         </is>
       </c>
     </row>
     <row r="54" ht="15" customHeight="1" s="26">
-      <c r="H54" s="36" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="J54" s="36" t="n">
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Buff</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
         <v>2</v>
       </c>
-      <c r="K54" s="36" t="inlineStr">
-        <is>
-          <t>技能强化</t>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Buff</t>
         </is>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1" s="26">
-      <c r="H55" s="36" t="inlineStr">
-        <is>
-          <t>Projectile</t>
-        </is>
-      </c>
-      <c r="J55" s="36" t="n">
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Aura</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
         <v>3</v>
       </c>
-      <c r="K55" s="36" t="inlineStr">
-        <is>
-          <t>弹道强化</t>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>??</t>
         </is>
       </c>
     </row>
     <row r="56" ht="15" customHeight="1" s="26">
-      <c r="H56" s="36" t="inlineStr">
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>4</v>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>TemporaryEffect</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>5</v>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>????</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="15" customHeight="1" s="26">
+      <c r="H58" t="inlineStr">
         <is>
           <t>Trigger</t>
         </is>
       </c>
-      <c r="J56" s="36" t="n">
-        <v>4</v>
-      </c>
-      <c r="K56" s="36" t="inlineStr">
-        <is>
-          <t>触发器强化</t>
-        </is>
-      </c>
-    </row>
-    <row r="57"/>
-    <row r="58" ht="15" customHeight="1" s="26">
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Battle.SkillModifierType</t>
-        </is>
-      </c>
-      <c r="C58">
+      <c r="J58" t="n">
+        <v>6</v>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>???</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="15" customHeight="1" s="26"/>
+    <row r="60" ht="15" customHeight="1" s="26">
+      <c r="B60" s="36" t="inlineStr">
+        <is>
+          <t>Battle.ModifierTargetType</t>
+        </is>
+      </c>
+      <c r="C60" s="36">
         <f>FALSE()</f>
         <v/>
       </c>
-      <c r="D58">
+      <c r="D60" s="36">
         <f>TRUE()</f>
         <v/>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>??????</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
+      <c r="F60" s="36" t="inlineStr">
+        <is>
+          <t>强化目标类型</t>
+        </is>
+      </c>
+      <c r="H60" s="36" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="J58" t="n">
+      <c r="J60" s="36" t="n">
         <v>0</v>
       </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="15" customHeight="1" s="26">
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>ProjectileNum</t>
-        </is>
-      </c>
-      <c r="J59" t="n">
+      <c r="K60" s="36" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="H61" s="36" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="J61" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>??????</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="15" customHeight="1" s="26">
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>AttackSpeed</t>
-        </is>
-      </c>
-      <c r="J60" t="n">
+      <c r="K61" s="36" t="inlineStr">
+        <is>
+          <t>单位强化</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="15" customHeight="1" s="26">
+      <c r="H62" s="36" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="J62" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>????</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>CooldownReduction</t>
-        </is>
-      </c>
-      <c r="J61" t="n">
+      <c r="K62" s="36" t="inlineStr">
+        <is>
+          <t>技能强化</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="15" customHeight="1" s="26">
+      <c r="H63" s="36" t="inlineStr">
+        <is>
+          <t>Projectile</t>
+        </is>
+      </c>
+      <c r="J63" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>????</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="15" customHeight="1" s="26"/>
-    <row r="63" ht="15" customHeight="1" s="26">
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Battle.ProjectileModifierType</t>
-        </is>
-      </c>
-      <c r="C63">
+      <c r="K63" s="36" t="inlineStr">
+        <is>
+          <t>弹道强化</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="15" customHeight="1" s="26">
+      <c r="H64" s="36" t="inlineStr">
+        <is>
+          <t>Trigger</t>
+        </is>
+      </c>
+      <c r="J64" s="36" t="n">
+        <v>4</v>
+      </c>
+      <c r="K64" s="36" t="inlineStr">
+        <is>
+          <t>触发器强化</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="15" customHeight="1" s="26"/>
+    <row r="66" ht="15" customHeight="1" s="26">
+      <c r="B66" s="36" t="inlineStr">
+        <is>
+          <t>Battle.SkillModifierType</t>
+        </is>
+      </c>
+      <c r="C66" s="36">
         <f>FALSE()</f>
         <v/>
       </c>
-      <c r="D63">
+      <c r="D66" s="36">
         <f>TRUE()</f>
         <v/>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="F66" s="36" t="inlineStr">
         <is>
           <t>??????</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="H66" s="36" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="J63" t="n">
+      <c r="J66" s="36" t="n">
         <v>0</v>
       </c>
-      <c r="K63" t="inlineStr">
+      <c r="K66" s="36" t="inlineStr">
         <is>
           <t>?</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="15" customHeight="1" s="26">
-      <c r="H64" t="inlineStr">
+    <row r="67" ht="15" customHeight="1" s="26">
+      <c r="H67" s="36" t="inlineStr">
+        <is>
+          <t>ProjectileNum</t>
+        </is>
+      </c>
+      <c r="J67" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="K67" s="36" t="inlineStr">
+        <is>
+          <t>??????</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="15" customHeight="1" s="26">
+      <c r="H68" s="36" t="inlineStr">
+        <is>
+          <t>AttackSpeed</t>
+        </is>
+      </c>
+      <c r="J68" s="36" t="n">
+        <v>2</v>
+      </c>
+      <c r="K68" s="36" t="inlineStr">
+        <is>
+          <t>????</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="H69" s="36" t="inlineStr">
+        <is>
+          <t>CooldownReduction</t>
+        </is>
+      </c>
+      <c r="J69" s="36" t="n">
+        <v>3</v>
+      </c>
+      <c r="K69" s="36" t="inlineStr">
+        <is>
+          <t>????</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="15" customHeight="1" s="26"/>
+    <row r="71" ht="15" customHeight="1" s="26">
+      <c r="B71" s="36" t="inlineStr">
+        <is>
+          <t>Battle.ProjectileModifierType</t>
+        </is>
+      </c>
+      <c r="C71" s="36">
+        <f>FALSE()</f>
+        <v/>
+      </c>
+      <c r="D71" s="36">
+        <f>TRUE()</f>
+        <v/>
+      </c>
+      <c r="F71" s="36" t="inlineStr">
+        <is>
+          <t>??????</t>
+        </is>
+      </c>
+      <c r="H71" s="36" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J71" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" s="36" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="15" customHeight="1" s="26">
+      <c r="H72" s="36" t="inlineStr">
         <is>
           <t>ReplaceProjectile</t>
         </is>
       </c>
-      <c r="J64" t="n">
+      <c r="J72" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="K64" t="inlineStr">
+      <c r="K72" s="36" t="inlineStr">
         <is>
           <t>??????</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="15" customHeight="1" s="26">
-      <c r="H65" t="inlineStr">
+    <row r="73" ht="15" customHeight="1" s="26">
+      <c r="H73" s="36" t="inlineStr">
         <is>
           <t>ProjectilePierce</t>
         </is>
       </c>
-      <c r="J65" t="n">
+      <c r="J73" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="K65" t="inlineStr">
+      <c r="K73" s="36" t="inlineStr">
         <is>
           <t>??????</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="15" customHeight="1" s="26">
-      <c r="H66" t="inlineStr">
+    <row r="74">
+      <c r="H74" s="36" t="inlineStr">
         <is>
           <t>ProjectileHitArea</t>
         </is>
       </c>
-      <c r="J66" t="n">
+      <c r="J74" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="K66" t="inlineStr">
+      <c r="K74" s="36" t="inlineStr">
         <is>
           <t>??????</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="15" customHeight="1" s="26"/>
-    <row r="68" ht="15" customHeight="1" s="26"/>
-    <row r="70" ht="15" customHeight="1" s="26"/>
-    <row r="71" ht="15" customHeight="1" s="26"/>
-    <row r="72" ht="15" customHeight="1" s="26"/>
-    <row r="73" ht="15" customHeight="1" s="26"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>

--- a/Excels/Excels/__enums__.xlsx
+++ b/Excels/Excels/__enums__.xlsx
@@ -2747,7 +2747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:L74"/>
+  <dimension ref="A1:L88"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.51953125" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="10" customWidth="1" style="44" min="1" max="1"/>
@@ -3758,123 +3758,123 @@
     </row>
     <row r="51"/>
     <row r="52" ht="15" customHeight="1" s="26">
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="36" t="inlineStr">
         <is>
           <t>Battle.ModifierSourceType</t>
         </is>
       </c>
-      <c r="C52">
+      <c r="C52" s="36">
         <f>FALSE()</f>
         <v/>
       </c>
-      <c r="D52">
+      <c r="D52" s="36">
         <f>TRUE()</f>
         <v/>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="F52" s="36" t="inlineStr">
         <is>
           <t>??????</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="H52" s="36" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="J52" t="n">
+      <c r="J52" s="36" t="n">
         <v>0</v>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="K52" s="36" t="inlineStr">
         <is>
           <t>?</t>
         </is>
       </c>
     </row>
     <row r="53" ht="15" customHeight="1" s="26">
-      <c r="H53" t="inlineStr">
+      <c r="H53" s="36" t="inlineStr">
         <is>
           <t>RogueEnhancement</t>
         </is>
       </c>
-      <c r="J53" t="n">
+      <c r="J53" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="K53" s="36" t="inlineStr">
         <is>
           <t>????</t>
         </is>
       </c>
     </row>
     <row r="54" ht="15" customHeight="1" s="26">
-      <c r="H54" t="inlineStr">
+      <c r="H54" s="36" t="inlineStr">
         <is>
           <t>Buff</t>
         </is>
       </c>
-      <c r="J54" t="n">
+      <c r="J54" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="K54" s="36" t="inlineStr">
         <is>
           <t>Buff</t>
         </is>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1" s="26">
-      <c r="H55" t="inlineStr">
+      <c r="H55" s="36" t="inlineStr">
         <is>
           <t>Aura</t>
         </is>
       </c>
-      <c r="J55" t="n">
+      <c r="J55" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="K55" s="36" t="inlineStr">
         <is>
           <t>??</t>
         </is>
       </c>
     </row>
     <row r="56" ht="15" customHeight="1" s="26">
-      <c r="H56" t="inlineStr">
+      <c r="H56" s="36" t="inlineStr">
         <is>
           <t>Equipment</t>
         </is>
       </c>
-      <c r="J56" t="n">
+      <c r="J56" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="K56" s="36" t="inlineStr">
         <is>
           <t>??</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="H57" t="inlineStr">
+      <c r="H57" s="36" t="inlineStr">
         <is>
           <t>TemporaryEffect</t>
         </is>
       </c>
-      <c r="J57" t="n">
+      <c r="J57" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="K57" s="36" t="inlineStr">
         <is>
           <t>????</t>
         </is>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1" s="26">
-      <c r="H58" t="inlineStr">
+      <c r="H58" s="36" t="inlineStr">
         <is>
           <t>Trigger</t>
         </is>
       </c>
-      <c r="J58" t="n">
+      <c r="J58" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="K58" s="36" t="inlineStr">
         <is>
           <t>???</t>
         </is>
@@ -4129,6 +4129,220 @@
       <c r="K74" s="36" t="inlineStr">
         <is>
           <t>??????</t>
+        </is>
+      </c>
+    </row>
+    <row r="75"/>
+    <row r="76">
+      <c r="B76" s="36" t="inlineStr">
+        <is>
+          <t>Battle.TriggerEventType</t>
+        </is>
+      </c>
+      <c r="F76" s="36" t="inlineStr">
+        <is>
+          <t>??????</t>
+        </is>
+      </c>
+      <c r="H76" s="36" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I76" s="36" t="n"/>
+      <c r="J76" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="H77" s="36" t="inlineStr">
+        <is>
+          <t>OnSkillCast</t>
+        </is>
+      </c>
+      <c r="I77" s="36" t="n"/>
+      <c r="J77" t="n">
+        <v>1</v>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>?????</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="H78" s="36" t="inlineStr">
+        <is>
+          <t>OnProjectileHit</t>
+        </is>
+      </c>
+      <c r="I78" s="36" t="n"/>
+      <c r="J78" t="n">
+        <v>2</v>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>?????</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="H79" s="36" t="inlineStr">
+        <is>
+          <t>OnKill</t>
+        </is>
+      </c>
+      <c r="I79" s="36" t="n"/>
+      <c r="J79" t="n">
+        <v>3</v>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>???</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="H80" s="36" t="inlineStr">
+        <is>
+          <t>OnBuffTick</t>
+        </is>
+      </c>
+      <c r="I80" s="36" t="n"/>
+      <c r="J80" t="n">
+        <v>4</v>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Buff???</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="H81" s="36" t="inlineStr">
+        <is>
+          <t>OnInterval</t>
+        </is>
+      </c>
+      <c r="I81" s="36" t="n"/>
+      <c r="J81" t="n">
+        <v>5</v>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>????</t>
+        </is>
+      </c>
+    </row>
+    <row r="82"/>
+    <row r="83">
+      <c r="B83" s="36" t="inlineStr">
+        <is>
+          <t>Battle.TriggerModifierType</t>
+        </is>
+      </c>
+      <c r="F83" s="36" t="inlineStr">
+        <is>
+          <t>??????</t>
+        </is>
+      </c>
+      <c r="H83" s="36" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I83" s="36" t="n"/>
+      <c r="J83" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="H84" s="36" t="inlineStr">
+        <is>
+          <t>AddEffect</t>
+        </is>
+      </c>
+      <c r="I84" s="36" t="n"/>
+      <c r="J84" t="n">
+        <v>1</v>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>????</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="H85" s="36" t="inlineStr">
+        <is>
+          <t>CastSkill</t>
+        </is>
+      </c>
+      <c r="I85" s="36" t="n"/>
+      <c r="J85" t="n">
+        <v>2</v>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>????</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="H86" s="36" t="inlineStr">
+        <is>
+          <t>AddBuff</t>
+        </is>
+      </c>
+      <c r="I86" s="36" t="n"/>
+      <c r="J86" t="n">
+        <v>3</v>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>??Buff</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="H87" s="36" t="inlineStr">
+        <is>
+          <t>RefreshCooldown</t>
+        </is>
+      </c>
+      <c r="I87" s="36" t="n"/>
+      <c r="J87" t="n">
+        <v>4</v>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>????</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="H88" s="36" t="inlineStr">
+        <is>
+          <t>AddProjectile</t>
+        </is>
+      </c>
+      <c r="I88" s="36" t="n"/>
+      <c r="J88" t="n">
+        <v>5</v>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>????</t>
         </is>
       </c>
     </row>

--- a/Excels/Excels/__enums__.xlsx
+++ b/Excels/Excels/__enums__.xlsx
@@ -2747,7 +2747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:L88"/>
+  <dimension ref="A1:L93"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.51953125" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="10" customWidth="1" style="44" min="1" max="1"/>
@@ -4150,10 +4150,10 @@
         </is>
       </c>
       <c r="I76" s="36" t="n"/>
-      <c r="J76" t="n">
+      <c r="J76" s="36" t="n">
         <v>0</v>
       </c>
-      <c r="K76" t="inlineStr">
+      <c r="K76" s="36" t="inlineStr">
         <is>
           <t>?</t>
         </is>
@@ -4166,10 +4166,10 @@
         </is>
       </c>
       <c r="I77" s="36" t="n"/>
-      <c r="J77" t="n">
+      <c r="J77" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="K77" t="inlineStr">
+      <c r="K77" s="36" t="inlineStr">
         <is>
           <t>?????</t>
         </is>
@@ -4182,10 +4182,10 @@
         </is>
       </c>
       <c r="I78" s="36" t="n"/>
-      <c r="J78" t="n">
+      <c r="J78" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="K78" t="inlineStr">
+      <c r="K78" s="36" t="inlineStr">
         <is>
           <t>?????</t>
         </is>
@@ -4198,10 +4198,10 @@
         </is>
       </c>
       <c r="I79" s="36" t="n"/>
-      <c r="J79" t="n">
+      <c r="J79" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="K79" t="inlineStr">
+      <c r="K79" s="36" t="inlineStr">
         <is>
           <t>???</t>
         </is>
@@ -4214,10 +4214,10 @@
         </is>
       </c>
       <c r="I80" s="36" t="n"/>
-      <c r="J80" t="n">
+      <c r="J80" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="K80" t="inlineStr">
+      <c r="K80" s="36" t="inlineStr">
         <is>
           <t>Buff???</t>
         </is>
@@ -4230,10 +4230,10 @@
         </is>
       </c>
       <c r="I81" s="36" t="n"/>
-      <c r="J81" t="n">
+      <c r="J81" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="K81" t="inlineStr">
+      <c r="K81" s="36" t="inlineStr">
         <is>
           <t>????</t>
         </is>
@@ -4257,10 +4257,10 @@
         </is>
       </c>
       <c r="I83" s="36" t="n"/>
-      <c r="J83" t="n">
+      <c r="J83" s="36" t="n">
         <v>0</v>
       </c>
-      <c r="K83" t="inlineStr">
+      <c r="K83" s="36" t="inlineStr">
         <is>
           <t>?</t>
         </is>
@@ -4273,10 +4273,10 @@
         </is>
       </c>
       <c r="I84" s="36" t="n"/>
-      <c r="J84" t="n">
+      <c r="J84" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="K84" t="inlineStr">
+      <c r="K84" s="36" t="inlineStr">
         <is>
           <t>????</t>
         </is>
@@ -4289,10 +4289,10 @@
         </is>
       </c>
       <c r="I85" s="36" t="n"/>
-      <c r="J85" t="n">
+      <c r="J85" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="K85" t="inlineStr">
+      <c r="K85" s="36" t="inlineStr">
         <is>
           <t>????</t>
         </is>
@@ -4305,10 +4305,10 @@
         </is>
       </c>
       <c r="I86" s="36" t="n"/>
-      <c r="J86" t="n">
+      <c r="J86" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="K86" t="inlineStr">
+      <c r="K86" s="36" t="inlineStr">
         <is>
           <t>??Buff</t>
         </is>
@@ -4321,10 +4321,10 @@
         </is>
       </c>
       <c r="I87" s="36" t="n"/>
-      <c r="J87" t="n">
+      <c r="J87" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="K87" t="inlineStr">
+      <c r="K87" s="36" t="inlineStr">
         <is>
           <t>????</t>
         </is>
@@ -4337,12 +4337,82 @@
         </is>
       </c>
       <c r="I88" s="36" t="n"/>
-      <c r="J88" t="n">
+      <c r="J88" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="K88" t="inlineStr">
+      <c r="K88" s="36" t="inlineStr">
         <is>
           <t>????</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Battle.EnhancementRarity</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>????</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="J90" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="J91" t="n">
+        <v>1</v>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="J92" t="n">
+        <v>2</v>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+      <c r="J93" t="n">
+        <v>3</v>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>??</t>
         </is>
       </c>
     </row>
